--- a/docs/downloads/04/tbl_age_obs_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/04/tbl_age_obs_alaotra_ambohidrony.xlsx
@@ -495,12 +495,6 @@
           <t>61-70 ans</t>
         </is>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
